--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -401,7 +401,7 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>Practitioner.meta.versionId</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10695" uniqueCount="942">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2407,7 +2407,7 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:code}
 </t>
   </si>
   <si>
@@ -2467,7 +2467,10 @@
     <t>Coded representation of the qualification.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
+    <t>Specific qualification the practitioner has to provide a service.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
   </si>
   <si>
     <t>./Qualifications.Value</t>
@@ -2663,6 +2666,10 @@
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>closed</t>
   </si>
   <si>
@@ -2676,6 +2683,9 @@
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.text</t>
@@ -2764,10 +2774,6 @@
     <t>Practitioner.qualification:exercicePro.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
   </si>
   <si>
@@ -2819,7 +2825,7 @@
     <t>savoirFaire</t>
   </si>
   <si>
-    <t>savoirFaire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.id</t>
@@ -28048,11 +28054,13 @@
         <v>78</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y213" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="Y213" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z213" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -28094,7 +28102,7 @@
         <v>770</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>78</v>
@@ -28102,10 +28110,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28131,14 +28139,14 @@
         <v>253</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28187,7 +28195,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28208,10 +28216,10 @@
         <v>78</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28219,10 +28227,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28248,10 +28256,10 @@
         <v>536</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -28302,7 +28310,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28323,7 +28331,7 @@
         <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN215" t="s" s="2">
         <v>78</v>
@@ -28334,13 +28342,13 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>764</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D216" t="s" s="2">
         <v>78</v>
@@ -28365,7 +28373,7 @@
         <v>765</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M216" t="s" s="2">
         <v>767</v>
@@ -28451,7 +28459,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>772</v>
@@ -28566,7 +28574,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>773</v>
@@ -28679,13 +28687,13 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>773</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>78</v>
@@ -28707,13 +28715,13 @@
         <v>78</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -28796,10 +28804,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28911,10 +28919,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29028,13 +29036,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B222" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="B222" t="s" s="2">
-        <v>812</v>
-      </c>
       <c r="C222" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>78</v>
@@ -29145,10 +29153,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29260,10 +29268,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29375,10 +29383,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29418,7 +29426,7 @@
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="S225" t="s" s="2">
         <v>78</v>
@@ -29492,10 +29500,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29555,7 +29563,7 @@
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>78</v>
@@ -29605,13 +29613,13 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D227" t="s" s="2">
         <v>78</v>
@@ -29722,10 +29730,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29837,10 +29845,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29952,10 +29960,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29995,7 +30003,7 @@
       </c>
       <c r="Q230" s="2"/>
       <c r="R230" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="S230" t="s" s="2">
         <v>78</v>
@@ -30069,10 +30077,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30132,7 +30140,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>78</v>
@@ -30182,13 +30190,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30299,10 +30307,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30414,10 +30422,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30529,10 +30537,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30572,7 +30580,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30646,10 +30654,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30709,7 +30717,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30759,10 +30767,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30802,7 +30810,7 @@
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="S237" t="s" s="2">
         <v>78</v>
@@ -30876,10 +30884,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -30991,7 +30999,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>774</v>
@@ -31110,7 +31118,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>779</v>
@@ -31227,7 +31235,7 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>784</v>
@@ -31286,11 +31294,13 @@
         <v>78</v>
       </c>
       <c r="X241" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y241" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="Y241" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z241" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31332,7 +31342,7 @@
         <v>770</v>
       </c>
       <c r="AN241" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO241" t="s" s="2">
         <v>78</v>
@@ -31340,10 +31350,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31455,10 +31465,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31549,7 +31559,7 @@
         <v>80</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>119</v>
@@ -31561,7 +31571,7 @@
         <v>78</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>78</v>
@@ -31572,10 +31582,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31647,14 +31657,14 @@
         <v>78</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>768</v>
+        <v>853</v>
       </c>
       <c r="AC244" s="2"/>
       <c r="AD244" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AF244" t="s" s="2">
         <v>458</v>
@@ -31666,7 +31676,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>102</v>
@@ -31689,13 +31699,13 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D245" t="s" s="2">
         <v>78</v>
@@ -31758,7 +31768,7 @@
       </c>
       <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>78</v>
@@ -31785,7 +31795,7 @@
         <v>80</v>
       </c>
       <c r="AI245" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ245" t="s" s="2">
         <v>102</v>
@@ -31808,13 +31818,13 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D246" t="s" s="2">
         <v>78</v>
@@ -31877,7 +31887,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>787</v>
+        <v>859</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -31904,7 +31914,7 @@
         <v>80</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -31927,10 +31937,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32023,7 +32033,7 @@
         <v>90</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>102</v>
@@ -32046,10 +32056,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32075,14 +32085,14 @@
         <v>253</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>78</v>
@@ -32131,7 +32141,7 @@
         <v>78</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>79</v>
@@ -32152,10 +32162,10 @@
         <v>78</v>
       </c>
       <c r="AM248" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN248" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO248" t="s" s="2">
         <v>78</v>
@@ -32163,10 +32173,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32278,10 +32288,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32395,10 +32405,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32424,7 +32434,7 @@
         <v>260</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="M251" t="s" s="2">
         <v>262</v>
@@ -32512,10 +32522,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32541,7 +32551,7 @@
         <v>260</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="M252" t="s" s="2">
         <v>271</v>
@@ -32631,10 +32641,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32657,13 +32667,13 @@
         <v>78</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -32714,7 +32724,7 @@
         <v>78</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>79</v>
@@ -32735,7 +32745,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32746,13 +32756,13 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>764</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>78</v>
@@ -32777,7 +32787,7 @@
         <v>765</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="M254" t="s" s="2">
         <v>767</v>
@@ -32863,7 +32873,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>772</v>
@@ -32978,7 +32988,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>773</v>
@@ -33095,7 +33105,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>774</v>
@@ -33214,7 +33224,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>779</v>
@@ -33331,7 +33341,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>784</v>
@@ -33390,11 +33400,13 @@
         <v>78</v>
       </c>
       <c r="X259" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y259" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="Y259" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z259" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>78</v>
@@ -33436,7 +33448,7 @@
         <v>770</v>
       </c>
       <c r="AN259" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO259" t="s" s="2">
         <v>78</v>
@@ -33444,10 +33456,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33559,10 +33571,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33653,7 +33665,7 @@
         <v>80</v>
       </c>
       <c r="AI261" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ261" t="s" s="2">
         <v>119</v>
@@ -33665,7 +33677,7 @@
         <v>78</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>78</v>
@@ -33676,10 +33688,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33751,14 +33763,14 @@
         <v>78</v>
       </c>
       <c r="AB262" t="s" s="2">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="AC262" s="2"/>
       <c r="AD262" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE262" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AF262" t="s" s="2">
         <v>458</v>
@@ -33770,7 +33782,7 @@
         <v>80</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ262" t="s" s="2">
         <v>102</v>
@@ -33793,13 +33805,13 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D263" t="s" s="2">
         <v>78</v>
@@ -33824,7 +33836,7 @@
         <v>154</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="M263" t="s" s="2">
         <v>455</v>
@@ -33862,7 +33874,7 @@
       </c>
       <c r="Y263" s="2"/>
       <c r="Z263" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>78</v>
@@ -33889,7 +33901,7 @@
         <v>80</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ263" t="s" s="2">
         <v>102</v>
@@ -33912,10 +33924,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C264" t="s" s="2">
         <v>337</v>
@@ -33943,7 +33955,7 @@
         <v>154</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="M264" t="s" s="2">
         <v>455</v>
@@ -34008,7 +34020,7 @@
         <v>80</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>102</v>
@@ -34031,10 +34043,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34127,7 +34139,7 @@
         <v>90</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ265" t="s" s="2">
         <v>102</v>
@@ -34150,10 +34162,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34179,14 +34191,14 @@
         <v>253</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>78</v>
@@ -34235,7 +34247,7 @@
         <v>78</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>79</v>
@@ -34256,10 +34268,10 @@
         <v>78</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN266" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO266" t="s" s="2">
         <v>78</v>
@@ -34267,10 +34279,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34382,10 +34394,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34499,10 +34511,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34528,7 +34540,7 @@
         <v>260</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="M269" t="s" s="2">
         <v>262</v>
@@ -34616,10 +34628,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34645,7 +34657,7 @@
         <v>260</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="M270" t="s" s="2">
         <v>271</v>
@@ -34735,10 +34747,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34764,10 +34776,10 @@
         <v>536</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" s="2"/>
@@ -34818,7 +34830,7 @@
         <v>78</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>79</v>
@@ -34839,7 +34851,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34850,13 +34862,13 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>764</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D272" t="s" s="2">
         <v>78</v>
@@ -34881,7 +34893,7 @@
         <v>765</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="M272" t="s" s="2">
         <v>767</v>
@@ -34967,7 +34979,7 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>772</v>
@@ -35082,7 +35094,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>773</v>
@@ -35199,7 +35211,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>774</v>
@@ -35318,7 +35330,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>779</v>
@@ -35435,7 +35447,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>784</v>
@@ -35494,11 +35506,13 @@
         <v>78</v>
       </c>
       <c r="X277" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y277" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="Y277" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z277" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>78</v>
@@ -35531,7 +35545,7 @@
         <v>102</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AL277" t="s" s="2">
         <v>78</v>
@@ -35540,7 +35554,7 @@
         <v>770</v>
       </c>
       <c r="AN277" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO277" t="s" s="2">
         <v>78</v>
@@ -35548,10 +35562,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35663,10 +35677,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35757,7 +35771,7 @@
         <v>80</v>
       </c>
       <c r="AI279" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ279" t="s" s="2">
         <v>119</v>
@@ -35769,7 +35783,7 @@
         <v>78</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>78</v>
@@ -35780,10 +35794,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35855,7 +35869,7 @@
         <v>78</v>
       </c>
       <c r="AB280" t="s" s="2">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="AC280" s="2"/>
       <c r="AD280" t="s" s="2">
@@ -35874,7 +35888,7 @@
         <v>80</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>102</v>
@@ -35897,13 +35911,13 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D281" t="s" s="2">
         <v>78</v>
@@ -35928,7 +35942,7 @@
         <v>154</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="M281" t="s" s="2">
         <v>455</v>
@@ -35966,7 +35980,7 @@
       </c>
       <c r="Y281" s="2"/>
       <c r="Z281" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>78</v>
@@ -35993,7 +36007,7 @@
         <v>80</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ281" t="s" s="2">
         <v>102</v>
@@ -36016,13 +36030,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36047,7 +36061,7 @@
         <v>154</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>455</v>
@@ -36085,7 +36099,7 @@
       </c>
       <c r="Y282" s="2"/>
       <c r="Z282" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>78</v>
@@ -36112,7 +36126,7 @@
         <v>80</v>
       </c>
       <c r="AI282" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ282" t="s" s="2">
         <v>102</v>
@@ -36135,10 +36149,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36231,7 +36245,7 @@
         <v>90</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ283" t="s" s="2">
         <v>102</v>
@@ -36254,10 +36268,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36283,14 +36297,14 @@
         <v>253</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P284" t="s" s="2">
         <v>78</v>
@@ -36339,7 +36353,7 @@
         <v>78</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>79</v>
@@ -36360,10 +36374,10 @@
         <v>78</v>
       </c>
       <c r="AM284" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN284" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO284" t="s" s="2">
         <v>78</v>
@@ -36371,10 +36385,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -36486,10 +36500,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36603,10 +36617,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36632,7 +36646,7 @@
         <v>260</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="M287" t="s" s="2">
         <v>262</v>
@@ -36703,7 +36717,7 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>266</v>
@@ -36720,10 +36734,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36749,7 +36763,7 @@
         <v>260</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="M288" t="s" s="2">
         <v>271</v>
@@ -36822,7 +36836,7 @@
         <v>102</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>275</v>
@@ -36839,10 +36853,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -36868,10 +36882,10 @@
         <v>536</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -36922,7 +36936,7 @@
         <v>78</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>79</v>
@@ -36943,7 +36957,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -36954,10 +36968,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -36980,19 +36994,19 @@
         <v>78</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="O290" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="P290" t="s" s="2">
         <v>78</v>
@@ -37021,7 +37035,7 @@
       </c>
       <c r="Y290" s="2"/>
       <c r="Z290" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="AA290" t="s" s="2">
         <v>78</v>
@@ -37039,7 +37053,7 @@
         <v>78</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>79</v>
@@ -37057,10 +37071,10 @@
         <v>78</v>
       </c>
       <c r="AL290" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="AM290" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="AN290" t="s" s="2">
         <v>78</v>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -27431,7 +27431,7 @@
         <v>80</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>78</v>
@@ -28361,7 +28361,7 @@
         <v>80</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>78</v>
